--- a/data/trans_orig/P15E_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26117</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>46091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46850</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -1299,97 +1299,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>946</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>70,5%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -1755,97 +1755,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16885</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>28692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42826</t>
+          <t>42915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15102</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>44021</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56871</t>
+          <t>56072</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63008</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78135</t>
+          <t>77930</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26696</t>
+          <t>28267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,22 +848,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14793</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>16975</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>44096</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>38058</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46091</t>
+          <t>49390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46300</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59321</t>
+          <t>63692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13944</t>
+          <t>14933</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -1863,27 +1863,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28692</t>
+          <t>29959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>34537</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42915</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50613</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44021</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56072</t>
+          <t>61591</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>77555</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77930</t>
+          <t>86200</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>68,17%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>88336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
